--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_141_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_141_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2805</v>
+        <v>6.9936</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4777</v>
+        <v>5.863</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8028</v>
+        <v>1.1307</v>
       </c>
       <c r="G2" t="n">
         <v>4.2612</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1791</v>
+        <v>0.8922</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.326</v>
+        <v>0.0593</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5051</v>
+        <v>0.8329</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0158</v>
+        <v>4.9752</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7257</v>
+        <v>3.3154</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2901</v>
+        <v>1.6598</v>
       </c>
       <c r="G3" t="n">
         <v>3.62</v>
@@ -688,13 +688,13 @@
         <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3</v>
+        <v>0.6594</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4402</v>
+        <v>0.1496</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1401</v>
+        <v>0.5098</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0717</v>
+        <v>3.5281</v>
       </c>
       <c r="E4" t="n">
-        <v>2.965</v>
+        <v>3.0086</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1067</v>
+        <v>0.5195</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.092</v>
+        <v>0.1072</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0958</v>
+        <v>1.2112</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1878</v>
+        <v>-1.104</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9804</v>
+        <v>0.8974</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6392</v>
+        <v>1.5733</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3412</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0724</v>
+        <v>-0.7902</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4566</v>
+        <v>-0.3621</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.529</v>
+        <v>-0.4281</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1454</v>
+        <v>1.3719</v>
       </c>
       <c r="T4" t="n">
-        <v>2.8941</v>
+        <v>0.6137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2513</v>
+        <v>0.7582</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5697</v>
+        <v>0.4254</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5697</v>
+        <v>1.4975</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9399</v>
+        <v>3.0752</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1516</v>
+        <v>1.9063</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7884</v>
+        <v>1.1689</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1072</v>
+        <v>-0.439</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2112</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.104</v>
+        <v>0.1372</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8974</v>
+        <v>-0.4209</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5733</v>
+        <v>0.1715</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.5924</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7902</v>
+        <v>-0.0181</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3621</v>
+        <v>-0.7477</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4281</v>
+        <v>0.7296</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7837</v>
+        <v>0.6919</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2434</v>
+        <v>0.6647</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0271</v>
+        <v>0.0272</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4254</v>
+        <v>2.8223</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4975</v>
+        <v>2.8223</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4211</v>
+        <v>1.5952</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5211</v>
+        <v>1.1524</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.4428</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.439</v>
+        <v>-0.092</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5760999999999999</v>
+        <v>1.0958</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1372</v>
+        <v>-1.1878</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4209</v>
+        <v>0.9804</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1715</v>
+        <v>0.6392</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5924</v>
+        <v>0.3412</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0181</v>
+        <v>-1.0724</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7477</v>
+        <v>0.4566</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7296</v>
+        <v>-1.529</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0378</v>
+        <v>1.6689</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2794</v>
+        <v>1.0815</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2416</v>
+        <v>0.5874</v>
       </c>
       <c r="V6" t="n">
-        <v>2.8223</v>
+        <v>2.5697</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8223</v>
+        <v>2.5697</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3709</v>
+        <v>-0.1275</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0825</v>
+        <v>-1.7719</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7116</v>
+        <v>1.6444</v>
       </c>
       <c r="G7" t="n">
         <v>-0.07829999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1713</v>
+        <v>0.4147</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2908</v>
+        <v>0.0198</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4621</v>
+        <v>0.3949</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.1573</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3243</v>
+        <v>-1.1396</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6343</v>
+        <v>0.9823</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9011</v>
+        <v>1.6962</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5760999999999999</v>
+        <v>0.3878</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.325</v>
+        <v>1.3084</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1398</v>
+        <v>0.9243</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5007</v>
+        <v>0.9243</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7613</v>
+        <v>0.7719</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0755</v>
+        <v>-0.5365</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6859</v>
+        <v>1.3084</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>1.907</v>
+        <v>0.2161</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9752</v>
+        <v>0.2557</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9318</v>
+        <v>-0.0395</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-2.0488</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.686</v>
+        <v>-3.2389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8479</v>
+        <v>1.1901</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6962</v>
+        <v>-0.6767</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3878</v>
+        <v>0.819</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3084</v>
+        <v>-1.4957</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9243</v>
+        <v>-0.9196</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9243</v>
+        <v>0.1512</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.0709</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7719</v>
+        <v>0.2429</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5365</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3084</v>
+        <v>-0.4248</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3917</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4648</v>
+        <v>0.4835</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2908</v>
+        <v>0.0002</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.174</v>
+        <v>0.4832</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2515</v>
+        <v>-2.0869</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3105</v>
+        <v>-2.15</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9411</v>
+        <v>0.063</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4574</v>
+        <v>-1.9011</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3901</v>
+        <v>-0.5760999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0673</v>
+        <v>-1.325</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-1.1398</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6855</v>
+        <v>-0.5007</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0368</v>
+        <v>-0.6391</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8087</v>
+        <v>-0.7613</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7045</v>
+        <v>-0.0755</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1041</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2781</v>
+        <v>0.51</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3383</v>
+        <v>0.1496</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0602</v>
+        <v>0.3605</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5133</v>
+        <v>-2.4538</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0074</v>
+        <v>-0.5464</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5059</v>
+        <v>-1.9075</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3759</v>
+        <v>-2.4574</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1069</v>
+        <v>-1.3901</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4828</v>
+        <v>-1.0673</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1963</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3396</v>
+        <v>-0.6855</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5359</v>
+        <v>0.0368</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1796</v>
+        <v>-1.8087</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2327</v>
+        <v>-0.7045</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9469</v>
+        <v>-1.1041</v>
       </c>
       <c r="P11" t="n">
         <v>0.4639</v>
@@ -1312,28 +1312,28 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2183</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1889</v>
+        <v>0.1024</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0294</v>
+        <v>-0.0266</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8197</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8197</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9821</v>
+        <v>-2.4633</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9033</v>
+        <v>-1.1254</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9212</v>
+        <v>-1.3379</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6767</v>
+        <v>-2.3759</v>
       </c>
       <c r="H12" t="n">
-        <v>0.819</v>
+        <v>0.1069</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4957</v>
+        <v>-2.4828</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9196</v>
+        <v>-1.1963</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1512</v>
+        <v>0.3396</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0709</v>
+        <v>-1.5359</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2429</v>
+        <v>-1.1796</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6677999999999999</v>
+        <v>-0.2327</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4248</v>
+        <v>-0.9469</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4498</v>
+        <v>0.2684</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6642</v>
+        <v>0.0709</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2144</v>
+        <v>0.1975</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="13">
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.08299999999999</v>
+        <v>10.8297</v>
       </c>
       <c r="E13" t="n">
-        <v>4.527099999999999</v>
+        <v>5.273499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.556</v>
+        <v>5.556099999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6642</v>
+        <v>1.664200000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>8.7576</v>
+        <v>8.757599999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.093300000000001</v>
+        <v>-7.0933</v>
       </c>
       <c r="J13" t="n">
-        <v>6.365900000000002</v>
+        <v>6.365900000000001</v>
       </c>
       <c r="K13" t="n">
         <v>9.997300000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-1.2397</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.461799999999999</v>
+        <v>-3.4618</v>
       </c>
       <c r="P13" t="n">
         <v>-3.479200000000001</v>
@@ -1468,10 +1468,10 @@
         <v>9.278200000000002</v>
       </c>
       <c r="S13" t="n">
-        <v>6.506100000000001</v>
+        <v>7.2528</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4205</v>
+        <v>3.1674</v>
       </c>
       <c r="U13" t="n">
         <v>4.0855</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6633</v>
+        <v>5.3425</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3644</v>
+        <v>3.7183</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2989</v>
+        <v>1.6242</v>
       </c>
       <c r="G14" t="n">
         <v>4.6981</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7332</v>
+        <v>-0.054</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4832</v>
+        <v>-0.1294</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.25</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9282</v>
+        <v>0.8717</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5996</v>
+        <v>3.1277</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6714</v>
+        <v>-2.256</v>
       </c>
       <c r="G15" t="n">
         <v>4.3063</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6796</v>
+        <v>-0.736</v>
       </c>
       <c r="T15" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.3848</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.3512</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0026</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6959</v>
+        <v>-0.2796</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7967</v>
+        <v>-1.7576</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1008</v>
+        <v>1.478</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.537</v>
+        <v>0.8091</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3301</v>
+        <v>-4.0024</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7931</v>
+        <v>4.8115</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.172</v>
+        <v>0.2703</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3929</v>
+        <v>-2.5502</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2208</v>
+        <v>2.8205</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.365</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9373</v>
+        <v>-1.4522</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5723</v>
+        <v>1.991</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7103</v>
+        <v>-1.4624</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6247</v>
+        <v>-1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0857</v>
+        <v>-0.4525</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1446</v>
+        <v>-0.5722</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4653</v>
+        <v>-0.7967</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3207</v>
+        <v>0.2245</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8091</v>
+        <v>-0.537</v>
       </c>
       <c r="H18" t="n">
-        <v>-4.0024</v>
+        <v>-1.3301</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8115</v>
+        <v>0.7931</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2703</v>
+        <v>-0.172</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.5502</v>
+        <v>-0.3929</v>
       </c>
       <c r="L18" t="n">
-        <v>2.8205</v>
+        <v>0.2208</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5387999999999999</v>
+        <v>-0.365</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4522</v>
+        <v>-0.9373</v>
       </c>
       <c r="O18" t="n">
-        <v>1.991</v>
+        <v>0.5723</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.3274</v>
+        <v>-0.5867</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.7177</v>
+        <v>-0.6247</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6097</v>
+        <v>0.038</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1935</v>
+        <v>-2.2549</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6541</v>
+        <v>-0.6584</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5394</v>
+        <v>-1.5964</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4093</v>
+        <v>-0.8656</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.994</v>
+        <v>-0.0961</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4153</v>
+        <v>-0.7695</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6268</v>
+        <v>0.6821</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9509</v>
+        <v>0.6085</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7825</v>
+        <v>-1.5477</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0431</v>
+        <v>-0.7045</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.8431</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3602</v>
+        <v>-0.1779</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0272</v>
+        <v>-0.1808</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3875</v>
+        <v>0.0029</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.262</v>
+        <v>-2.3787</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6918</v>
+        <v>-1.772</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5702</v>
+        <v>-0.6066</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3083</v>
+        <v>-2.4093</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9002</v>
+        <v>-0.994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4081</v>
+        <v>-1.4153</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9957</v>
+        <v>-1.6268</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2457</v>
+        <v>-0.9509</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2414</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3126</v>
+        <v>-0.7825</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.146</v>
+        <v>-0.0431</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8333</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P20" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5979</v>
+        <v>0.1751</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2864</v>
+        <v>-0.1452</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3115</v>
+        <v>0.3203</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0336</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2689</v>
+        <v>-2.4021</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1819</v>
+        <v>-1.0457</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9129</v>
+        <v>-1.3565</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7616</v>
+        <v>-2.3083</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1859</v>
+        <v>-1.9002</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5757</v>
+        <v>-0.4081</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1862</v>
+        <v>-0.9957</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9341</v>
+        <v>0.2457</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2521</v>
+        <v>-1.2414</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4246</v>
+        <v>-1.3126</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2518</v>
+        <v>-2.146</v>
       </c>
       <c r="O21" t="n">
-        <v>1.6764</v>
+        <v>0.8333</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>0.315</v>
+        <v>-0.738</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0044</v>
+        <v>-0.6403</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3106</v>
+        <v>-0.0977</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.214</v>
+        <v>-0.2836</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-2.0336</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4965</v>
+        <v>-3.0939</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7764</v>
+        <v>-3.7716</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7201</v>
+        <v>0.6777</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8656</v>
+        <v>-2.7616</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0961</v>
+        <v>-2.1859</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7695</v>
+        <v>-0.5757</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6821</v>
+        <v>-3.1862</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6085</v>
+        <v>-0.9341</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0736</v>
+        <v>-2.2521</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5477</v>
+        <v>0.4246</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7045</v>
+        <v>-1.2518</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8431</v>
+        <v>1.6764</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4195</v>
+        <v>-0.51</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>-0.5854</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1208</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2836</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2836</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7704</v>
+        <v>-3.9004</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9538</v>
+        <v>-2.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8166</v>
+        <v>-1.3004</v>
       </c>
       <c r="G23" t="n">
         <v>-2.753</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7133</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9744</v>
+        <v>-0.4582</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.083</v>
+        <v>-8.510299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.555999999999999</v>
+        <v>-5.556</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.5271</v>
+        <v>-2.9542</v>
       </c>
       <c r="G24" t="n">
         <v>-1.664</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.757400000000001</v>
+        <v>-8.757399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>7.093399999999999</v>
+        <v>7.093400000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7018</v>
+        <v>4.701800000000001</v>
       </c>
       <c r="K24" t="n">
         <v>1.2398</v>
       </c>
       <c r="L24" t="n">
-        <v>3.461899999999999</v>
+        <v>3.461899999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-6.3659</v>
@@ -2314,25 +2314,25 @@
         <v>-9.997299999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>3.631400000000001</v>
+        <v>3.6314</v>
       </c>
       <c r="P24" t="n">
         <v>3.4793</v>
       </c>
       <c r="Q24" t="n">
-        <v>-9.278200000000002</v>
+        <v>-9.2782</v>
       </c>
       <c r="R24" t="n">
         <v>12.7575</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.506</v>
+        <v>-4.9331</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.0854</v>
+        <v>-4.085699999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.4206</v>
+        <v>-0.8478000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-5.3921</v>
